--- a/SHINHWA_QMS_WORKFLOW/07_AUDIT/고객심사/SQ_증빙매핑표_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/07_AUDIT/고객심사/SQ_증빙매핑표_20261008.xlsx
@@ -622,12 +622,12 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>취업규칙 연계 후보(키워드 추정)</t>
+          <t>취업규칙 관련도(키워드 추정)</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>취업규칙 조항</t>
+          <t>취업규칙 조항(2026-09-28 검토 반영본)</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -759,11 +759,7 @@
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="4" t="inlineStr">
         <is>
@@ -871,11 +867,7 @@
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="4" t="inlineStr">
         <is>
@@ -983,11 +975,7 @@
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="4" t="inlineStr">
         <is>
@@ -1087,11 +1075,7 @@
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="5" t="inlineStr">
         <is>
@@ -1195,11 +1179,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr"/>
       <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="4" t="inlineStr">
         <is>
@@ -1309,11 +1289,7 @@
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="4" t="inlineStr">
         <is>
@@ -1413,11 +1389,7 @@
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S11" s="3" t="inlineStr"/>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="6" t="inlineStr">
         <is>
@@ -1521,11 +1493,7 @@
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="4" t="inlineStr">
         <is>
@@ -1629,11 +1597,7 @@
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S13" s="3" t="inlineStr"/>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="4" t="inlineStr">
         <is>
@@ -1741,11 +1705,7 @@
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="4" t="inlineStr">
         <is>
@@ -1855,11 +1815,7 @@
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S15" s="3" t="inlineStr"/>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="4" t="inlineStr">
         <is>
@@ -1967,11 +1923,7 @@
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S16" s="3" t="inlineStr"/>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="4" t="inlineStr">
         <is>
@@ -2058,16 +2010,8 @@
           <t>부적합품 관리 프로세스 이미지 번역본.png</t>
         </is>
       </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>후보(키워드: 교육, 작업자)</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr"/>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="5" t="inlineStr">
         <is>
@@ -2159,11 +2103,7 @@
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S18" s="3" t="inlineStr"/>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="5" t="inlineStr">
         <is>
@@ -2259,11 +2199,7 @@
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S19" s="3" t="inlineStr"/>
       <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="5" t="inlineStr">
         <is>
@@ -2361,11 +2297,7 @@
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S20" s="3" t="inlineStr"/>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="4" t="inlineStr">
         <is>
@@ -2473,11 +2405,7 @@
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S21" s="3" t="inlineStr"/>
       <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="4" t="inlineStr">
         <is>
@@ -2581,11 +2509,7 @@
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="4" t="inlineStr">
         <is>
@@ -2681,11 +2605,7 @@
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="inlineStr"/>
       <c r="U23" s="5" t="inlineStr">
         <is>
@@ -2789,11 +2709,7 @@
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr"/>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S24" s="3" t="inlineStr"/>
       <c r="T24" s="3" t="inlineStr"/>
       <c r="U24" s="4" t="inlineStr">
         <is>
@@ -2893,11 +2809,7 @@
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr"/>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S25" s="3" t="inlineStr"/>
       <c r="T25" s="3" t="inlineStr"/>
       <c r="U25" s="4" t="inlineStr">
         <is>
@@ -3004,11 +2916,7 @@
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S26" s="3" t="inlineStr"/>
       <c r="T26" s="3" t="inlineStr"/>
       <c r="U26" s="6" t="inlineStr">
         <is>
@@ -3100,11 +3008,7 @@
       </c>
       <c r="Q27" s="3" t="inlineStr"/>
       <c r="R27" s="3" t="inlineStr"/>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S27" s="3" t="inlineStr"/>
       <c r="T27" s="3" t="inlineStr"/>
       <c r="U27" s="4" t="inlineStr">
         <is>
@@ -3192,11 +3096,7 @@
       </c>
       <c r="Q28" s="3" t="inlineStr"/>
       <c r="R28" s="3" t="inlineStr"/>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S28" s="3" t="inlineStr"/>
       <c r="T28" s="3" t="inlineStr"/>
       <c r="U28" s="5" t="inlineStr">
         <is>
@@ -3284,11 +3184,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr"/>
       <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S29" s="3" t="inlineStr"/>
       <c r="T29" s="3" t="inlineStr"/>
       <c r="U29" s="6" t="inlineStr">
         <is>
@@ -3380,11 +3276,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr"/>
       <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="inlineStr"/>
       <c r="U30" s="6" t="inlineStr">
         <is>
@@ -3476,11 +3368,7 @@
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr"/>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S31" s="3" t="inlineStr"/>
       <c r="T31" s="3" t="inlineStr"/>
       <c r="U31" s="4" t="inlineStr">
         <is>
@@ -3572,11 +3460,7 @@
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr"/>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="inlineStr"/>
       <c r="U32" s="4" t="inlineStr">
         <is>
@@ -3664,11 +3548,7 @@
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
       <c r="R33" s="3" t="inlineStr"/>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S33" s="3" t="inlineStr"/>
       <c r="T33" s="3" t="inlineStr"/>
       <c r="U33" s="4" t="inlineStr">
         <is>
@@ -3778,11 +3658,7 @@
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S34" s="3" t="inlineStr"/>
       <c r="T34" s="3" t="inlineStr"/>
       <c r="U34" s="4" t="inlineStr">
         <is>
@@ -3887,11 +3763,7 @@
       </c>
       <c r="Q35" s="3" t="inlineStr"/>
       <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S35" s="3" t="inlineStr"/>
       <c r="T35" s="3" t="inlineStr"/>
       <c r="U35" s="4" t="inlineStr">
         <is>
@@ -3995,11 +3867,7 @@
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S36" s="3" t="inlineStr"/>
       <c r="T36" s="3" t="inlineStr"/>
       <c r="U36" s="4" t="inlineStr">
         <is>
@@ -4103,11 +3971,7 @@
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S37" s="3" t="inlineStr"/>
       <c r="T37" s="3" t="inlineStr"/>
       <c r="U37" s="4" t="inlineStr">
         <is>
@@ -4207,11 +4071,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr"/>
       <c r="R38" s="3" t="inlineStr"/>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="inlineStr"/>
       <c r="U38" s="4" t="inlineStr">
         <is>
@@ -4311,11 +4171,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr"/>
       <c r="R39" s="3" t="inlineStr"/>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="inlineStr"/>
       <c r="U39" s="4" t="inlineStr">
         <is>
@@ -4419,11 +4275,7 @@
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr"/>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S40" s="3" t="inlineStr"/>
       <c r="T40" s="3" t="inlineStr"/>
       <c r="U40" s="4" t="inlineStr">
         <is>
@@ -4515,11 +4367,7 @@
       </c>
       <c r="Q41" s="3" t="inlineStr"/>
       <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S41" s="3" t="inlineStr"/>
       <c r="T41" s="3" t="inlineStr"/>
       <c r="U41" s="4" t="inlineStr">
         <is>
@@ -4625,11 +4473,7 @@
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr"/>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S42" s="3" t="inlineStr"/>
       <c r="T42" s="3" t="inlineStr"/>
       <c r="U42" s="4" t="inlineStr">
         <is>
@@ -4729,11 +4573,7 @@
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr"/>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="4" t="inlineStr">
         <is>
@@ -4829,11 +4669,7 @@
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr"/>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="4" t="inlineStr">
         <is>
@@ -4921,11 +4757,7 @@
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S45" s="3" t="inlineStr"/>
       <c r="T45" s="3" t="inlineStr"/>
       <c r="U45" s="5" t="inlineStr">
         <is>
@@ -5021,11 +4853,7 @@
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr"/>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S46" s="3" t="inlineStr"/>
       <c r="T46" s="3" t="inlineStr"/>
       <c r="U46" s="5" t="inlineStr">
         <is>
@@ -5127,11 +4955,7 @@
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr"/>
-      <c r="S47" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S47" s="3" t="inlineStr"/>
       <c r="T47" s="3" t="inlineStr"/>
       <c r="U47" s="4" t="inlineStr">
         <is>
@@ -5239,11 +5063,7 @@
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr"/>
-      <c r="S48" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S48" s="3" t="inlineStr"/>
       <c r="T48" s="3" t="inlineStr"/>
       <c r="U48" s="4" t="inlineStr">
         <is>
@@ -5335,11 +5155,7 @@
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr"/>
-      <c r="S49" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S49" s="3" t="inlineStr"/>
       <c r="T49" s="3" t="inlineStr"/>
       <c r="U49" s="6" t="inlineStr">
         <is>
@@ -5447,11 +5263,7 @@
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr"/>
-      <c r="S50" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S50" s="3" t="inlineStr"/>
       <c r="T50" s="3" t="inlineStr"/>
       <c r="U50" s="4" t="inlineStr">
         <is>
@@ -5545,11 +5357,7 @@
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr"/>
-      <c r="S51" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S51" s="3" t="inlineStr"/>
       <c r="T51" s="3" t="inlineStr"/>
       <c r="U51" s="6" t="inlineStr">
         <is>
@@ -5645,11 +5453,7 @@
       </c>
       <c r="Q52" s="3" t="inlineStr"/>
       <c r="R52" s="3" t="inlineStr"/>
-      <c r="S52" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S52" s="3" t="inlineStr"/>
       <c r="T52" s="3" t="inlineStr"/>
       <c r="U52" s="6" t="inlineStr">
         <is>
@@ -5749,11 +5553,7 @@
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr"/>
-      <c r="S53" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S53" s="3" t="inlineStr"/>
       <c r="T53" s="3" t="inlineStr"/>
       <c r="U53" s="4" t="inlineStr">
         <is>
@@ -5849,11 +5649,7 @@
       </c>
       <c r="Q54" s="3" t="inlineStr"/>
       <c r="R54" s="3" t="inlineStr"/>
-      <c r="S54" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S54" s="3" t="inlineStr"/>
       <c r="T54" s="3" t="inlineStr"/>
       <c r="U54" s="4" t="inlineStr">
         <is>
@@ -5955,11 +5751,7 @@
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr"/>
-      <c r="S55" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S55" s="3" t="inlineStr"/>
       <c r="T55" s="3" t="inlineStr"/>
       <c r="U55" s="5" t="inlineStr">
         <is>
@@ -6067,11 +5859,7 @@
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr"/>
-      <c r="S56" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S56" s="3" t="inlineStr"/>
       <c r="T56" s="3" t="inlineStr"/>
       <c r="U56" s="4" t="inlineStr">
         <is>
@@ -6179,11 +5967,7 @@
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr"/>
-      <c r="S57" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S57" s="3" t="inlineStr"/>
       <c r="T57" s="3" t="inlineStr"/>
       <c r="U57" s="4" t="inlineStr">
         <is>
@@ -6291,11 +6075,7 @@
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr"/>
-      <c r="S58" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S58" s="3" t="inlineStr"/>
       <c r="T58" s="3" t="inlineStr"/>
       <c r="U58" s="4" t="inlineStr">
         <is>
@@ -6399,11 +6179,7 @@
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr"/>
-      <c r="S59" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S59" s="3" t="inlineStr"/>
       <c r="T59" s="3" t="inlineStr"/>
       <c r="U59" s="4" t="inlineStr">
         <is>
@@ -6511,11 +6287,7 @@
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr"/>
-      <c r="S60" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S60" s="3" t="inlineStr"/>
       <c r="T60" s="3" t="inlineStr"/>
       <c r="U60" s="4" t="inlineStr">
         <is>
@@ -6623,11 +6395,7 @@
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr"/>
-      <c r="S61" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S61" s="3" t="inlineStr"/>
       <c r="T61" s="3" t="inlineStr"/>
       <c r="U61" s="4" t="inlineStr">
         <is>
@@ -6735,11 +6503,7 @@
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr"/>
-      <c r="S62" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S62" s="3" t="inlineStr"/>
       <c r="T62" s="3" t="inlineStr"/>
       <c r="U62" s="4" t="inlineStr">
         <is>
@@ -6847,11 +6611,7 @@
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr"/>
-      <c r="S63" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S63" s="3" t="inlineStr"/>
       <c r="T63" s="3" t="inlineStr"/>
       <c r="U63" s="4" t="inlineStr">
         <is>
@@ -6959,11 +6719,7 @@
         </is>
       </c>
       <c r="R64" s="3" t="inlineStr"/>
-      <c r="S64" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S64" s="3" t="inlineStr"/>
       <c r="T64" s="3" t="inlineStr"/>
       <c r="U64" s="4" t="inlineStr">
         <is>
@@ -7071,11 +6827,7 @@
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr"/>
-      <c r="S65" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S65" s="3" t="inlineStr"/>
       <c r="T65" s="3" t="inlineStr"/>
       <c r="U65" s="4" t="inlineStr">
         <is>
@@ -7185,11 +6937,7 @@
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr"/>
-      <c r="S66" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S66" s="3" t="inlineStr"/>
       <c r="T66" s="3" t="inlineStr"/>
       <c r="U66" s="4" t="inlineStr">
         <is>
@@ -7297,11 +7045,7 @@
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr"/>
-      <c r="S67" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S67" s="3" t="inlineStr"/>
       <c r="T67" s="3" t="inlineStr"/>
       <c r="U67" s="4" t="inlineStr">
         <is>
@@ -7408,16 +7152,8 @@
           <t>게이지 R&amp;R  측정 시트  .pptx.xlsx</t>
         </is>
       </c>
-      <c r="R68" s="3" t="inlineStr">
-        <is>
-          <t>후보(키워드: 작업자)</t>
-        </is>
-      </c>
-      <c r="S68" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="R68" s="3" t="inlineStr"/>
+      <c r="S68" s="3" t="inlineStr"/>
       <c r="T68" s="3" t="inlineStr"/>
       <c r="U68" s="4" t="inlineStr">
         <is>
@@ -7519,11 +7255,7 @@
         </is>
       </c>
       <c r="R69" s="3" t="inlineStr"/>
-      <c r="S69" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S69" s="3" t="inlineStr"/>
       <c r="T69" s="3" t="inlineStr"/>
       <c r="U69" s="6" t="inlineStr">
         <is>
@@ -7623,11 +7355,7 @@
         </is>
       </c>
       <c r="R70" s="3" t="inlineStr"/>
-      <c r="S70" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S70" s="3" t="inlineStr"/>
       <c r="T70" s="3" t="inlineStr"/>
       <c r="U70" s="6" t="inlineStr">
         <is>
@@ -7723,11 +7451,7 @@
       </c>
       <c r="Q71" s="3" t="inlineStr"/>
       <c r="R71" s="3" t="inlineStr"/>
-      <c r="S71" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S71" s="3" t="inlineStr"/>
       <c r="T71" s="3" t="inlineStr"/>
       <c r="U71" s="6" t="inlineStr">
         <is>
@@ -7827,11 +7551,7 @@
         </is>
       </c>
       <c r="R72" s="3" t="inlineStr"/>
-      <c r="S72" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S72" s="3" t="inlineStr"/>
       <c r="T72" s="3" t="inlineStr"/>
       <c r="U72" s="4" t="inlineStr">
         <is>
@@ -7930,16 +7650,8 @@
           <t>체크시트.xlsx</t>
         </is>
       </c>
-      <c r="R73" s="3" t="inlineStr">
-        <is>
-          <t>후보(키워드: 작업자)</t>
-        </is>
-      </c>
-      <c r="S73" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="R73" s="3" t="inlineStr"/>
+      <c r="S73" s="3" t="inlineStr"/>
       <c r="T73" s="3" t="inlineStr"/>
       <c r="U73" s="5" t="inlineStr">
         <is>
@@ -8039,11 +7751,7 @@
         </is>
       </c>
       <c r="R74" s="3" t="inlineStr"/>
-      <c r="S74" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S74" s="3" t="inlineStr"/>
       <c r="T74" s="3" t="inlineStr"/>
       <c r="U74" s="6" t="inlineStr">
         <is>
@@ -8139,11 +7847,7 @@
       </c>
       <c r="Q75" s="3" t="inlineStr"/>
       <c r="R75" s="3" t="inlineStr"/>
-      <c r="S75" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S75" s="3" t="inlineStr"/>
       <c r="T75" s="3" t="inlineStr"/>
       <c r="U75" s="6" t="inlineStr">
         <is>
@@ -8253,11 +7957,7 @@
         </is>
       </c>
       <c r="R76" s="3" t="inlineStr"/>
-      <c r="S76" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S76" s="3" t="inlineStr"/>
       <c r="T76" s="3" t="inlineStr"/>
       <c r="U76" s="4" t="inlineStr">
         <is>
@@ -8353,11 +8053,7 @@
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr"/>
-      <c r="S77" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S77" s="3" t="inlineStr"/>
       <c r="T77" s="3" t="inlineStr"/>
       <c r="U77" s="4" t="inlineStr">
         <is>
@@ -8453,11 +8149,7 @@
         </is>
       </c>
       <c r="R78" s="3" t="inlineStr"/>
-      <c r="S78" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S78" s="3" t="inlineStr"/>
       <c r="T78" s="3" t="inlineStr"/>
       <c r="U78" s="4" t="inlineStr">
         <is>
@@ -8553,11 +8245,7 @@
         </is>
       </c>
       <c r="R79" s="3" t="inlineStr"/>
-      <c r="S79" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S79" s="3" t="inlineStr"/>
       <c r="T79" s="3" t="inlineStr"/>
       <c r="U79" s="6" t="inlineStr">
         <is>
@@ -8653,11 +8341,7 @@
         </is>
       </c>
       <c r="R80" s="3" t="inlineStr"/>
-      <c r="S80" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S80" s="3" t="inlineStr"/>
       <c r="T80" s="3" t="inlineStr"/>
       <c r="U80" s="6" t="inlineStr">
         <is>
@@ -8745,11 +8429,7 @@
         </is>
       </c>
       <c r="R81" s="3" t="inlineStr"/>
-      <c r="S81" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S81" s="3" t="inlineStr"/>
       <c r="T81" s="3" t="inlineStr"/>
       <c r="U81" s="6" t="inlineStr">
         <is>
@@ -8857,11 +8537,7 @@
         </is>
       </c>
       <c r="R82" s="3" t="inlineStr"/>
-      <c r="S82" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S82" s="3" t="inlineStr"/>
       <c r="T82" s="3" t="inlineStr"/>
       <c r="U82" s="4" t="inlineStr">
         <is>
@@ -8953,11 +8629,7 @@
       </c>
       <c r="Q83" s="3" t="inlineStr"/>
       <c r="R83" s="3" t="inlineStr"/>
-      <c r="S83" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S83" s="3" t="inlineStr"/>
       <c r="T83" s="3" t="inlineStr"/>
       <c r="U83" s="4" t="inlineStr">
         <is>
@@ -9041,11 +8713,7 @@
       </c>
       <c r="Q84" s="3" t="inlineStr"/>
       <c r="R84" s="3" t="inlineStr"/>
-      <c r="S84" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S84" s="3" t="inlineStr"/>
       <c r="T84" s="3" t="inlineStr"/>
       <c r="U84" s="5" t="inlineStr">
         <is>
@@ -9137,11 +8805,7 @@
       </c>
       <c r="Q85" s="3" t="inlineStr"/>
       <c r="R85" s="3" t="inlineStr"/>
-      <c r="S85" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S85" s="3" t="inlineStr"/>
       <c r="T85" s="3" t="inlineStr"/>
       <c r="U85" s="4" t="inlineStr">
         <is>
@@ -9237,11 +8901,7 @@
         </is>
       </c>
       <c r="R86" s="3" t="inlineStr"/>
-      <c r="S86" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S86" s="3" t="inlineStr"/>
       <c r="T86" s="3" t="inlineStr"/>
       <c r="U86" s="4" t="inlineStr">
         <is>
@@ -9325,11 +8985,7 @@
       </c>
       <c r="Q87" s="3" t="inlineStr"/>
       <c r="R87" s="3" t="inlineStr"/>
-      <c r="S87" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S87" s="3" t="inlineStr"/>
       <c r="T87" s="3" t="inlineStr"/>
       <c r="U87" s="6" t="inlineStr">
         <is>
@@ -9421,11 +9077,7 @@
       </c>
       <c r="Q88" s="3" t="inlineStr"/>
       <c r="R88" s="3" t="inlineStr"/>
-      <c r="S88" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S88" s="3" t="inlineStr"/>
       <c r="T88" s="3" t="inlineStr"/>
       <c r="U88" s="6" t="inlineStr">
         <is>
@@ -9535,11 +9187,7 @@
         </is>
       </c>
       <c r="R89" s="3" t="inlineStr"/>
-      <c r="S89" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S89" s="3" t="inlineStr"/>
       <c r="T89" s="3" t="inlineStr"/>
       <c r="U89" s="4" t="inlineStr">
         <is>
@@ -9647,11 +9295,7 @@
         </is>
       </c>
       <c r="R90" s="3" t="inlineStr"/>
-      <c r="S90" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S90" s="3" t="inlineStr"/>
       <c r="T90" s="3" t="inlineStr"/>
       <c r="U90" s="4" t="inlineStr">
         <is>
@@ -9755,11 +9399,7 @@
       </c>
       <c r="Q91" s="3" t="inlineStr"/>
       <c r="R91" s="3" t="inlineStr"/>
-      <c r="S91" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S91" s="3" t="inlineStr"/>
       <c r="T91" s="3" t="inlineStr"/>
       <c r="U91" s="4" t="inlineStr">
         <is>
@@ -9847,11 +9487,7 @@
       </c>
       <c r="Q92" s="3" t="inlineStr"/>
       <c r="R92" s="3" t="inlineStr"/>
-      <c r="S92" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S92" s="3" t="inlineStr"/>
       <c r="T92" s="3" t="inlineStr"/>
       <c r="U92" s="6" t="inlineStr">
         <is>
@@ -9953,11 +9589,7 @@
         </is>
       </c>
       <c r="R93" s="3" t="inlineStr"/>
-      <c r="S93" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S93" s="3" t="inlineStr"/>
       <c r="T93" s="3" t="inlineStr"/>
       <c r="U93" s="4" t="inlineStr">
         <is>
@@ -10057,11 +9689,7 @@
         </is>
       </c>
       <c r="R94" s="3" t="inlineStr"/>
-      <c r="S94" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S94" s="3" t="inlineStr"/>
       <c r="T94" s="3" t="inlineStr"/>
       <c r="U94" s="4" t="inlineStr">
         <is>
@@ -10161,11 +9789,7 @@
         </is>
       </c>
       <c r="R95" s="3" t="inlineStr"/>
-      <c r="S95" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S95" s="3" t="inlineStr"/>
       <c r="T95" s="3" t="inlineStr"/>
       <c r="U95" s="4" t="inlineStr">
         <is>
@@ -10265,11 +9889,7 @@
         </is>
       </c>
       <c r="R96" s="3" t="inlineStr"/>
-      <c r="S96" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S96" s="3" t="inlineStr"/>
       <c r="T96" s="3" t="inlineStr"/>
       <c r="U96" s="4" t="inlineStr">
         <is>
@@ -10377,11 +9997,7 @@
         </is>
       </c>
       <c r="R97" s="3" t="inlineStr"/>
-      <c r="S97" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S97" s="3" t="inlineStr"/>
       <c r="T97" s="3" t="inlineStr"/>
       <c r="U97" s="4" t="inlineStr">
         <is>
@@ -10489,11 +10105,7 @@
         </is>
       </c>
       <c r="R98" s="3" t="inlineStr"/>
-      <c r="S98" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S98" s="3" t="inlineStr"/>
       <c r="T98" s="3" t="inlineStr"/>
       <c r="U98" s="4" t="inlineStr">
         <is>
@@ -10601,11 +10213,7 @@
         </is>
       </c>
       <c r="R99" s="3" t="inlineStr"/>
-      <c r="S99" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S99" s="3" t="inlineStr"/>
       <c r="T99" s="3" t="inlineStr"/>
       <c r="U99" s="4" t="inlineStr">
         <is>
@@ -10713,11 +10321,7 @@
         </is>
       </c>
       <c r="R100" s="3" t="inlineStr"/>
-      <c r="S100" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S100" s="3" t="inlineStr"/>
       <c r="T100" s="3" t="inlineStr"/>
       <c r="U100" s="4" t="inlineStr">
         <is>
@@ -10817,11 +10421,7 @@
         </is>
       </c>
       <c r="R101" s="3" t="inlineStr"/>
-      <c r="S101" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S101" s="3" t="inlineStr"/>
       <c r="T101" s="3" t="inlineStr"/>
       <c r="U101" s="4" t="inlineStr">
         <is>
@@ -10921,11 +10521,7 @@
         </is>
       </c>
       <c r="R102" s="3" t="inlineStr"/>
-      <c r="S102" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S102" s="3" t="inlineStr"/>
       <c r="T102" s="3" t="inlineStr"/>
       <c r="U102" s="4" t="inlineStr">
         <is>
@@ -11017,11 +10613,7 @@
         </is>
       </c>
       <c r="R103" s="3" t="inlineStr"/>
-      <c r="S103" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S103" s="3" t="inlineStr"/>
       <c r="T103" s="3" t="inlineStr"/>
       <c r="U103" s="6" t="inlineStr">
         <is>
@@ -11111,11 +10703,7 @@
       </c>
       <c r="Q104" s="3" t="inlineStr"/>
       <c r="R104" s="3" t="inlineStr"/>
-      <c r="S104" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S104" s="3" t="inlineStr"/>
       <c r="T104" s="3" t="inlineStr"/>
       <c r="U104" s="6" t="inlineStr">
         <is>
@@ -11203,11 +10791,7 @@
       </c>
       <c r="Q105" s="3" t="inlineStr"/>
       <c r="R105" s="3" t="inlineStr"/>
-      <c r="S105" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S105" s="3" t="inlineStr"/>
       <c r="T105" s="3" t="inlineStr"/>
       <c r="U105" s="6" t="inlineStr">
         <is>
@@ -11295,11 +10879,7 @@
       </c>
       <c r="Q106" s="3" t="inlineStr"/>
       <c r="R106" s="3" t="inlineStr"/>
-      <c r="S106" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S106" s="3" t="inlineStr"/>
       <c r="T106" s="3" t="inlineStr"/>
       <c r="U106" s="6" t="inlineStr">
         <is>
@@ -11403,11 +10983,7 @@
         </is>
       </c>
       <c r="R107" s="3" t="inlineStr"/>
-      <c r="S107" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S107" s="3" t="inlineStr"/>
       <c r="T107" s="3" t="inlineStr"/>
       <c r="U107" s="4" t="inlineStr">
         <is>
@@ -11495,11 +11071,7 @@
         </is>
       </c>
       <c r="R108" s="3" t="inlineStr"/>
-      <c r="S108" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S108" s="3" t="inlineStr"/>
       <c r="T108" s="3" t="inlineStr"/>
       <c r="U108" s="5" t="inlineStr">
         <is>
@@ -11583,11 +11155,7 @@
       </c>
       <c r="Q109" s="3" t="inlineStr"/>
       <c r="R109" s="3" t="inlineStr"/>
-      <c r="S109" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S109" s="3" t="inlineStr"/>
       <c r="T109" s="3" t="inlineStr"/>
       <c r="U109" s="5" t="inlineStr">
         <is>
@@ -11677,11 +11245,7 @@
       </c>
       <c r="Q110" s="3" t="inlineStr"/>
       <c r="R110" s="3" t="inlineStr"/>
-      <c r="S110" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S110" s="3" t="inlineStr"/>
       <c r="T110" s="3" t="inlineStr"/>
       <c r="U110" s="5" t="inlineStr">
         <is>
@@ -11769,11 +11333,7 @@
       </c>
       <c r="Q111" s="3" t="inlineStr"/>
       <c r="R111" s="3" t="inlineStr"/>
-      <c r="S111" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S111" s="3" t="inlineStr"/>
       <c r="T111" s="3" t="inlineStr"/>
       <c r="U111" s="5" t="inlineStr">
         <is>
@@ -11861,11 +11421,7 @@
       </c>
       <c r="Q112" s="3" t="inlineStr"/>
       <c r="R112" s="3" t="inlineStr"/>
-      <c r="S112" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S112" s="3" t="inlineStr"/>
       <c r="T112" s="3" t="inlineStr"/>
       <c r="U112" s="6" t="inlineStr">
         <is>
@@ -11970,11 +11526,7 @@
         </is>
       </c>
       <c r="R113" s="3" t="inlineStr"/>
-      <c r="S113" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S113" s="3" t="inlineStr"/>
       <c r="T113" s="3" t="inlineStr"/>
       <c r="U113" s="4" t="inlineStr">
         <is>
@@ -12070,11 +11622,7 @@
         </is>
       </c>
       <c r="R114" s="3" t="inlineStr"/>
-      <c r="S114" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S114" s="3" t="inlineStr"/>
       <c r="T114" s="3" t="inlineStr"/>
       <c r="U114" s="4" t="inlineStr">
         <is>
@@ -12170,11 +11718,7 @@
         </is>
       </c>
       <c r="R115" s="3" t="inlineStr"/>
-      <c r="S115" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S115" s="3" t="inlineStr"/>
       <c r="T115" s="3" t="inlineStr"/>
       <c r="U115" s="4" t="inlineStr">
         <is>
@@ -12270,11 +11814,7 @@
         </is>
       </c>
       <c r="R116" s="3" t="inlineStr"/>
-      <c r="S116" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S116" s="3" t="inlineStr"/>
       <c r="T116" s="3" t="inlineStr"/>
       <c r="U116" s="4" t="inlineStr">
         <is>
@@ -12379,11 +11919,7 @@
         </is>
       </c>
       <c r="R117" s="3" t="inlineStr"/>
-      <c r="S117" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S117" s="3" t="inlineStr"/>
       <c r="T117" s="3" t="inlineStr"/>
       <c r="U117" s="6" t="inlineStr">
         <is>
@@ -12487,11 +12023,7 @@
         </is>
       </c>
       <c r="R118" s="3" t="inlineStr"/>
-      <c r="S118" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S118" s="3" t="inlineStr"/>
       <c r="T118" s="3" t="inlineStr"/>
       <c r="U118" s="4" t="inlineStr">
         <is>
@@ -12587,11 +12119,7 @@
         </is>
       </c>
       <c r="R119" s="3" t="inlineStr"/>
-      <c r="S119" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S119" s="3" t="inlineStr"/>
       <c r="T119" s="3" t="inlineStr"/>
       <c r="U119" s="5" t="inlineStr">
         <is>
@@ -12695,11 +12223,7 @@
         </is>
       </c>
       <c r="R120" s="3" t="inlineStr"/>
-      <c r="S120" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S120" s="3" t="inlineStr"/>
       <c r="T120" s="3" t="inlineStr"/>
       <c r="U120" s="4" t="inlineStr">
         <is>
@@ -12803,11 +12327,7 @@
         </is>
       </c>
       <c r="R121" s="3" t="inlineStr"/>
-      <c r="S121" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S121" s="3" t="inlineStr"/>
       <c r="T121" s="3" t="inlineStr"/>
       <c r="U121" s="4" t="inlineStr">
         <is>
@@ -12911,11 +12431,7 @@
         </is>
       </c>
       <c r="R122" s="3" t="inlineStr"/>
-      <c r="S122" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S122" s="3" t="inlineStr"/>
       <c r="T122" s="3" t="inlineStr"/>
       <c r="U122" s="4" t="inlineStr">
         <is>
@@ -13021,11 +12537,7 @@
       </c>
       <c r="Q123" s="3" t="inlineStr"/>
       <c r="R123" s="3" t="inlineStr"/>
-      <c r="S123" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S123" s="3" t="inlineStr"/>
       <c r="T123" s="3" t="inlineStr"/>
       <c r="U123" s="4" t="inlineStr">
         <is>
@@ -13129,11 +12641,7 @@
       </c>
       <c r="Q124" s="3" t="inlineStr"/>
       <c r="R124" s="3" t="inlineStr"/>
-      <c r="S124" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S124" s="3" t="inlineStr"/>
       <c r="T124" s="3" t="inlineStr"/>
       <c r="U124" s="4" t="inlineStr">
         <is>
@@ -13237,11 +12745,7 @@
       </c>
       <c r="Q125" s="3" t="inlineStr"/>
       <c r="R125" s="3" t="inlineStr"/>
-      <c r="S125" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S125" s="3" t="inlineStr"/>
       <c r="T125" s="3" t="inlineStr"/>
       <c r="U125" s="4" t="inlineStr">
         <is>
@@ -13349,11 +12853,7 @@
         </is>
       </c>
       <c r="R126" s="3" t="inlineStr"/>
-      <c r="S126" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S126" s="3" t="inlineStr"/>
       <c r="T126" s="3" t="inlineStr"/>
       <c r="U126" s="4" t="inlineStr">
         <is>
@@ -13449,11 +12949,7 @@
       </c>
       <c r="Q127" s="3" t="inlineStr"/>
       <c r="R127" s="3" t="inlineStr"/>
-      <c r="S127" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S127" s="3" t="inlineStr"/>
       <c r="T127" s="3" t="inlineStr"/>
       <c r="U127" s="6" t="inlineStr">
         <is>
@@ -13563,11 +13059,7 @@
         </is>
       </c>
       <c r="R128" s="3" t="inlineStr"/>
-      <c r="S128" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S128" s="3" t="inlineStr"/>
       <c r="T128" s="3" t="inlineStr"/>
       <c r="U128" s="4" t="inlineStr">
         <is>
@@ -13675,11 +13167,7 @@
         </is>
       </c>
       <c r="R129" s="3" t="inlineStr"/>
-      <c r="S129" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S129" s="3" t="inlineStr"/>
       <c r="T129" s="3" t="inlineStr"/>
       <c r="U129" s="4" t="inlineStr">
         <is>
@@ -13777,11 +13265,7 @@
       </c>
       <c r="Q130" s="3" t="inlineStr"/>
       <c r="R130" s="3" t="inlineStr"/>
-      <c r="S130" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S130" s="3" t="inlineStr"/>
       <c r="T130" s="3" t="inlineStr"/>
       <c r="U130" s="6" t="inlineStr">
         <is>
@@ -13885,11 +13369,7 @@
       </c>
       <c r="Q131" s="3" t="inlineStr"/>
       <c r="R131" s="3" t="inlineStr"/>
-      <c r="S131" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S131" s="3" t="inlineStr"/>
       <c r="T131" s="3" t="inlineStr"/>
       <c r="U131" s="4" t="inlineStr">
         <is>
@@ -13993,11 +13473,7 @@
       </c>
       <c r="Q132" s="3" t="inlineStr"/>
       <c r="R132" s="3" t="inlineStr"/>
-      <c r="S132" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S132" s="3" t="inlineStr"/>
       <c r="T132" s="3" t="inlineStr"/>
       <c r="U132" s="4" t="inlineStr">
         <is>
@@ -14104,11 +13580,7 @@
       </c>
       <c r="Q133" s="3" t="inlineStr"/>
       <c r="R133" s="3" t="inlineStr"/>
-      <c r="S133" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S133" s="3" t="inlineStr"/>
       <c r="T133" s="3" t="inlineStr"/>
       <c r="U133" s="4" t="inlineStr">
         <is>
@@ -14208,11 +13680,7 @@
       </c>
       <c r="Q134" s="3" t="inlineStr"/>
       <c r="R134" s="3" t="inlineStr"/>
-      <c r="S134" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S134" s="3" t="inlineStr"/>
       <c r="T134" s="3" t="inlineStr"/>
       <c r="U134" s="4" t="inlineStr">
         <is>
@@ -14312,11 +13780,7 @@
       </c>
       <c r="Q135" s="3" t="inlineStr"/>
       <c r="R135" s="3" t="inlineStr"/>
-      <c r="S135" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S135" s="3" t="inlineStr"/>
       <c r="T135" s="3" t="inlineStr"/>
       <c r="U135" s="4" t="inlineStr">
         <is>
@@ -14422,11 +13886,7 @@
       </c>
       <c r="Q136" s="3" t="inlineStr"/>
       <c r="R136" s="3" t="inlineStr"/>
-      <c r="S136" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S136" s="3" t="inlineStr"/>
       <c r="T136" s="3" t="inlineStr"/>
       <c r="U136" s="4" t="inlineStr">
         <is>
@@ -14514,11 +13974,7 @@
       </c>
       <c r="Q137" s="3" t="inlineStr"/>
       <c r="R137" s="3" t="inlineStr"/>
-      <c r="S137" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S137" s="3" t="inlineStr"/>
       <c r="T137" s="3" t="inlineStr"/>
       <c r="U137" s="5" t="inlineStr">
         <is>
@@ -14622,11 +14078,7 @@
       </c>
       <c r="Q138" s="3" t="inlineStr"/>
       <c r="R138" s="3" t="inlineStr"/>
-      <c r="S138" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S138" s="3" t="inlineStr"/>
       <c r="T138" s="3" t="inlineStr"/>
       <c r="U138" s="4" t="inlineStr">
         <is>
@@ -14714,11 +14166,7 @@
       </c>
       <c r="Q139" s="3" t="inlineStr"/>
       <c r="R139" s="3" t="inlineStr"/>
-      <c r="S139" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S139" s="3" t="inlineStr"/>
       <c r="T139" s="3" t="inlineStr"/>
       <c r="U139" s="5" t="inlineStr">
         <is>
@@ -14806,11 +14254,7 @@
       </c>
       <c r="Q140" s="3" t="inlineStr"/>
       <c r="R140" s="3" t="inlineStr"/>
-      <c r="S140" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S140" s="3" t="inlineStr"/>
       <c r="T140" s="3" t="inlineStr"/>
       <c r="U140" s="5" t="inlineStr">
         <is>
@@ -14906,11 +14350,7 @@
       </c>
       <c r="Q141" s="3" t="inlineStr"/>
       <c r="R141" s="3" t="inlineStr"/>
-      <c r="S141" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S141" s="3" t="inlineStr"/>
       <c r="T141" s="3" t="inlineStr"/>
       <c r="U141" s="4" t="inlineStr">
         <is>
@@ -15006,11 +14446,7 @@
       </c>
       <c r="Q142" s="3" t="inlineStr"/>
       <c r="R142" s="3" t="inlineStr"/>
-      <c r="S142" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S142" s="3" t="inlineStr"/>
       <c r="T142" s="3" t="inlineStr"/>
       <c r="U142" s="4" t="inlineStr">
         <is>
@@ -15114,11 +14550,7 @@
       </c>
       <c r="Q143" s="3" t="inlineStr"/>
       <c r="R143" s="3" t="inlineStr"/>
-      <c r="S143" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S143" s="3" t="inlineStr"/>
       <c r="T143" s="3" t="inlineStr"/>
       <c r="U143" s="4" t="inlineStr">
         <is>
@@ -15214,11 +14646,7 @@
         </is>
       </c>
       <c r="R144" s="3" t="inlineStr"/>
-      <c r="S144" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S144" s="3" t="inlineStr"/>
       <c r="T144" s="3" t="inlineStr"/>
       <c r="U144" s="5" t="inlineStr">
         <is>
@@ -15328,11 +14756,7 @@
         </is>
       </c>
       <c r="R145" s="3" t="inlineStr"/>
-      <c r="S145" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S145" s="3" t="inlineStr"/>
       <c r="T145" s="3" t="inlineStr"/>
       <c r="U145" s="4" t="inlineStr">
         <is>
@@ -15428,11 +14852,7 @@
       </c>
       <c r="Q146" s="3" t="inlineStr"/>
       <c r="R146" s="3" t="inlineStr"/>
-      <c r="S146" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S146" s="3" t="inlineStr"/>
       <c r="T146" s="3" t="inlineStr"/>
       <c r="U146" s="6" t="inlineStr">
         <is>
@@ -15528,11 +14948,7 @@
       </c>
       <c r="Q147" s="3" t="inlineStr"/>
       <c r="R147" s="3" t="inlineStr"/>
-      <c r="S147" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S147" s="3" t="inlineStr"/>
       <c r="T147" s="3" t="inlineStr"/>
       <c r="U147" s="6" t="inlineStr">
         <is>
@@ -15632,11 +15048,7 @@
         </is>
       </c>
       <c r="R148" s="3" t="inlineStr"/>
-      <c r="S148" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S148" s="3" t="inlineStr"/>
       <c r="T148" s="3" t="inlineStr"/>
       <c r="U148" s="4" t="inlineStr">
         <is>
@@ -15724,11 +15136,7 @@
       </c>
       <c r="Q149" s="3" t="inlineStr"/>
       <c r="R149" s="3" t="inlineStr"/>
-      <c r="S149" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S149" s="3" t="inlineStr"/>
       <c r="T149" s="3" t="inlineStr"/>
       <c r="U149" s="5" t="inlineStr">
         <is>
@@ -15836,11 +15244,7 @@
         </is>
       </c>
       <c r="R150" s="3" t="inlineStr"/>
-      <c r="S150" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S150" s="3" t="inlineStr"/>
       <c r="T150" s="3" t="inlineStr"/>
       <c r="U150" s="4" t="inlineStr">
         <is>
@@ -15936,11 +15340,7 @@
         </is>
       </c>
       <c r="R151" s="3" t="inlineStr"/>
-      <c r="S151" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S151" s="3" t="inlineStr"/>
       <c r="T151" s="3" t="inlineStr"/>
       <c r="U151" s="5" t="inlineStr">
         <is>
@@ -16044,11 +15444,7 @@
         </is>
       </c>
       <c r="R152" s="3" t="inlineStr"/>
-      <c r="S152" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S152" s="3" t="inlineStr"/>
       <c r="T152" s="3" t="inlineStr"/>
       <c r="U152" s="4" t="inlineStr">
         <is>
@@ -16140,11 +15536,7 @@
       </c>
       <c r="Q153" s="3" t="inlineStr"/>
       <c r="R153" s="3" t="inlineStr"/>
-      <c r="S153" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S153" s="3" t="inlineStr"/>
       <c r="T153" s="3" t="inlineStr"/>
       <c r="U153" s="4" t="inlineStr">
         <is>
@@ -16236,11 +15628,7 @@
       </c>
       <c r="Q154" s="3" t="inlineStr"/>
       <c r="R154" s="3" t="inlineStr"/>
-      <c r="S154" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S154" s="3" t="inlineStr"/>
       <c r="T154" s="3" t="inlineStr"/>
       <c r="U154" s="4" t="inlineStr">
         <is>
@@ -16324,11 +15712,7 @@
       </c>
       <c r="Q155" s="3" t="inlineStr"/>
       <c r="R155" s="3" t="inlineStr"/>
-      <c r="S155" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S155" s="3" t="inlineStr"/>
       <c r="T155" s="3" t="inlineStr"/>
       <c r="U155" s="5" t="inlineStr">
         <is>
@@ -16432,11 +15816,7 @@
         </is>
       </c>
       <c r="R156" s="3" t="inlineStr"/>
-      <c r="S156" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S156" s="3" t="inlineStr"/>
       <c r="T156" s="3" t="inlineStr"/>
       <c r="U156" s="4" t="inlineStr">
         <is>
@@ -16532,11 +15912,7 @@
         </is>
       </c>
       <c r="R157" s="3" t="inlineStr"/>
-      <c r="S157" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S157" s="3" t="inlineStr"/>
       <c r="T157" s="3" t="inlineStr"/>
       <c r="U157" s="4" t="inlineStr">
         <is>
@@ -16646,11 +16022,7 @@
         </is>
       </c>
       <c r="R158" s="3" t="inlineStr"/>
-      <c r="S158" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S158" s="3" t="inlineStr"/>
       <c r="T158" s="3" t="inlineStr"/>
       <c r="U158" s="4" t="inlineStr">
         <is>
@@ -16742,11 +16114,7 @@
         </is>
       </c>
       <c r="R159" s="3" t="inlineStr"/>
-      <c r="S159" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S159" s="3" t="inlineStr"/>
       <c r="T159" s="3" t="inlineStr"/>
       <c r="U159" s="5" t="inlineStr">
         <is>
@@ -16846,11 +16214,7 @@
         </is>
       </c>
       <c r="R160" s="3" t="inlineStr"/>
-      <c r="S160" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S160" s="3" t="inlineStr"/>
       <c r="T160" s="3" t="inlineStr"/>
       <c r="U160" s="5" t="inlineStr">
         <is>
@@ -16950,11 +16314,7 @@
         </is>
       </c>
       <c r="R161" s="3" t="inlineStr"/>
-      <c r="S161" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S161" s="3" t="inlineStr"/>
       <c r="T161" s="3" t="inlineStr"/>
       <c r="U161" s="5" t="inlineStr">
         <is>
@@ -17042,11 +16402,7 @@
         </is>
       </c>
       <c r="R162" s="3" t="inlineStr"/>
-      <c r="S162" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S162" s="3" t="inlineStr"/>
       <c r="T162" s="3" t="inlineStr"/>
       <c r="U162" s="5" t="inlineStr">
         <is>
@@ -17144,11 +16500,7 @@
       </c>
       <c r="Q163" s="3" t="inlineStr"/>
       <c r="R163" s="3" t="inlineStr"/>
-      <c r="S163" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S163" s="3" t="inlineStr"/>
       <c r="T163" s="3" t="inlineStr"/>
       <c r="U163" s="4" t="inlineStr">
         <is>
@@ -17244,11 +16596,7 @@
       </c>
       <c r="Q164" s="3" t="inlineStr"/>
       <c r="R164" s="3" t="inlineStr"/>
-      <c r="S164" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S164" s="3" t="inlineStr"/>
       <c r="T164" s="3" t="inlineStr"/>
       <c r="U164" s="4" t="inlineStr">
         <is>
@@ -17352,11 +16700,7 @@
       </c>
       <c r="Q165" s="3" t="inlineStr"/>
       <c r="R165" s="3" t="inlineStr"/>
-      <c r="S165" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S165" s="3" t="inlineStr"/>
       <c r="T165" s="3" t="inlineStr"/>
       <c r="U165" s="4" t="inlineStr">
         <is>
@@ -17460,11 +16804,7 @@
       </c>
       <c r="Q166" s="3" t="inlineStr"/>
       <c r="R166" s="3" t="inlineStr"/>
-      <c r="S166" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S166" s="3" t="inlineStr"/>
       <c r="T166" s="3" t="inlineStr"/>
       <c r="U166" s="4" t="inlineStr">
         <is>
@@ -17568,11 +16908,7 @@
       </c>
       <c r="Q167" s="3" t="inlineStr"/>
       <c r="R167" s="3" t="inlineStr"/>
-      <c r="S167" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S167" s="3" t="inlineStr"/>
       <c r="T167" s="3" t="inlineStr"/>
       <c r="U167" s="4" t="inlineStr">
         <is>
@@ -17676,11 +17012,7 @@
       </c>
       <c r="Q168" s="3" t="inlineStr"/>
       <c r="R168" s="3" t="inlineStr"/>
-      <c r="S168" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S168" s="3" t="inlineStr"/>
       <c r="T168" s="3" t="inlineStr"/>
       <c r="U168" s="4" t="inlineStr">
         <is>
@@ -17791,15 +17123,19 @@
       </c>
       <c r="R169" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 작업자)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S169" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T169" s="3" t="inlineStr"/>
+          <t>제85조(안전보건관리규정), 제87조(위험기계·기구의 방호조치), 제88조(보호구의 지급 및 착용)</t>
+        </is>
+      </c>
+      <c r="T169" s="3" t="inlineStr">
+        <is>
+          <t>일반 안전 의무 근거. 개별 기준서·점검 기록은 별도 문서 필요</t>
+        </is>
+      </c>
       <c r="U169" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -17897,13 +17233,21 @@
           <t>3.안전보호장비 사용 기준서.xlsx</t>
         </is>
       </c>
-      <c r="R170" s="3" t="inlineStr"/>
+      <c r="R170" s="3" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
       <c r="S170" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T170" s="3" t="inlineStr"/>
+          <t>제85조(안전보건관리규정), 제87조(위험기계·기구의 방호조치), 제88조(보호구의 지급 및 착용)</t>
+        </is>
+      </c>
+      <c r="T170" s="3" t="inlineStr">
+        <is>
+          <t>일반 안전 의무 근거. 개별 기준서·점검 기록은 별도 문서 필요</t>
+        </is>
+      </c>
       <c r="U170" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -18001,13 +17345,21 @@
           <t>관리대장.xlsx</t>
         </is>
       </c>
-      <c r="R171" s="3" t="inlineStr"/>
+      <c r="R171" s="3" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
       <c r="S171" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T171" s="3" t="inlineStr"/>
+          <t>제85조(안전보건관리규정), 제87조(위험기계·기구의 방호조치), 제88조(보호구의 지급 및 착용)</t>
+        </is>
+      </c>
+      <c r="T171" s="3" t="inlineStr">
+        <is>
+          <t>일반 안전 의무 근거. 개별 기준서·점검 기록은 별도 문서 필요</t>
+        </is>
+      </c>
       <c r="U171" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -18107,15 +17459,19 @@
       </c>
       <c r="R172" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 교육)</t>
+          <t>직접</t>
         </is>
       </c>
       <c r="S172" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T172" s="3" t="inlineStr"/>
+          <t>제86조(안전보건 교육), 제85조(안전보건관리규정), 제67조(교육시간), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T172" s="3" t="inlineStr">
+        <is>
+          <t>안전교육은 제86조가 근거. 교안·실시보고서 등 기록 양식은 취업규칙에 없음 / 교육시간의 근로시간 처리·직무교육 의무만 규정. 교육 계획·이력 증빙은 취업규칙에 없음</t>
+        </is>
+      </c>
       <c r="U172" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -18215,15 +17571,19 @@
       </c>
       <c r="R173" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 교육, 작업자)</t>
+          <t>직접</t>
         </is>
       </c>
       <c r="S173" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T173" s="3" t="inlineStr"/>
+          <t>제86조(안전보건 교육), 제85조(안전보건관리규정), 제67조(교육시간), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T173" s="3" t="inlineStr">
+        <is>
+          <t>안전교육은 제86조가 근거. 교안·실시보고서 등 기록 양식은 취업규칙에 없음 / 교육시간의 근로시간 처리·직무교육 의무만 규정. 교육 계획·이력 증빙은 취업규칙에 없음</t>
+        </is>
+      </c>
       <c r="U173" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -18315,15 +17675,19 @@
       </c>
       <c r="R174" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 교육, 작업자)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S174" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T174" s="3" t="inlineStr"/>
+          <t>제85조(안전보건관리규정), 제86조(안전보건 교육)</t>
+        </is>
+      </c>
+      <c r="T174" s="3" t="inlineStr">
+        <is>
+          <t>수칙 게시·교육 근거. 라인별 수칙 내용은 별도 문서/현물</t>
+        </is>
+      </c>
       <c r="U174" s="7" t="inlineStr">
         <is>
           <t>D 현물 관리(양식 없음)</t>
@@ -18422,11 +17786,7 @@
         </is>
       </c>
       <c r="R175" s="3" t="inlineStr"/>
-      <c r="S175" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S175" s="3" t="inlineStr"/>
       <c r="T175" s="3" t="inlineStr"/>
       <c r="U175" s="4" t="inlineStr">
         <is>
@@ -18525,10 +17885,14 @@
           <t>MSDS 필요성 및 활용방법.pdf</t>
         </is>
       </c>
-      <c r="R176" s="3" t="inlineStr"/>
+      <c r="R176" s="3" t="inlineStr">
+        <is>
+          <t>직접</t>
+        </is>
+      </c>
       <c r="S176" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
+          <t>제89조(물질안전보건자료의 게시 및 교육)</t>
         </is>
       </c>
       <c r="T176" s="3" t="inlineStr"/>
@@ -18637,13 +18001,21 @@
           <t>1동_설비일상점검 (1).xlsx</t>
         </is>
       </c>
-      <c r="R177" s="3" t="inlineStr"/>
+      <c r="R177" s="3" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
       <c r="S177" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T177" s="3" t="inlineStr"/>
+          <t>제85조(안전보건관리규정), 제87조(위험기계·기구의 방호조치), 제88조(보호구의 지급 및 착용)</t>
+        </is>
+      </c>
+      <c r="T177" s="3" t="inlineStr">
+        <is>
+          <t>일반 안전 의무 근거. 개별 기준서·점검 기록은 별도 문서 필요</t>
+        </is>
+      </c>
       <c r="U177" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -18741,13 +18113,21 @@
           <t>안전관리.pptx</t>
         </is>
       </c>
-      <c r="R178" s="3" t="inlineStr"/>
+      <c r="R178" s="3" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
       <c r="S178" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T178" s="3" t="inlineStr"/>
+          <t>제85조(안전보건관리규정), 제87조(위험기계·기구의 방호조치), 제88조(보호구의 지급 및 착용)</t>
+        </is>
+      </c>
+      <c r="T178" s="3" t="inlineStr">
+        <is>
+          <t>일반 안전 의무 근거. 개별 기준서·점검 기록은 별도 문서 필요</t>
+        </is>
+      </c>
       <c r="U178" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -18854,11 +18234,7 @@
         </is>
       </c>
       <c r="R179" s="3" t="inlineStr"/>
-      <c r="S179" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S179" s="3" t="inlineStr"/>
       <c r="T179" s="3" t="inlineStr"/>
       <c r="U179" s="4" t="inlineStr">
         <is>
@@ -18954,11 +18330,7 @@
         </is>
       </c>
       <c r="R180" s="3" t="inlineStr"/>
-      <c r="S180" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S180" s="3" t="inlineStr"/>
       <c r="T180" s="3" t="inlineStr"/>
       <c r="U180" s="4" t="inlineStr">
         <is>
@@ -19060,11 +18432,7 @@
         </is>
       </c>
       <c r="R181" s="3" t="inlineStr"/>
-      <c r="S181" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S181" s="3" t="inlineStr"/>
       <c r="T181" s="3" t="inlineStr"/>
       <c r="U181" s="4" t="inlineStr">
         <is>
@@ -19172,11 +18540,7 @@
         </is>
       </c>
       <c r="R182" s="3" t="inlineStr"/>
-      <c r="S182" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S182" s="3" t="inlineStr"/>
       <c r="T182" s="3" t="inlineStr"/>
       <c r="U182" s="4" t="inlineStr">
         <is>
@@ -19284,11 +18648,7 @@
         </is>
       </c>
       <c r="R183" s="3" t="inlineStr"/>
-      <c r="S183" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S183" s="3" t="inlineStr"/>
       <c r="T183" s="3" t="inlineStr"/>
       <c r="U183" s="4" t="inlineStr">
         <is>
@@ -19396,11 +18756,7 @@
         </is>
       </c>
       <c r="R184" s="3" t="inlineStr"/>
-      <c r="S184" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S184" s="3" t="inlineStr"/>
       <c r="T184" s="3" t="inlineStr"/>
       <c r="U184" s="4" t="inlineStr">
         <is>
@@ -19502,11 +18858,7 @@
         </is>
       </c>
       <c r="R185" s="3" t="inlineStr"/>
-      <c r="S185" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S185" s="3" t="inlineStr"/>
       <c r="T185" s="3" t="inlineStr"/>
       <c r="U185" s="4" t="inlineStr">
         <is>
@@ -19614,11 +18966,7 @@
         </is>
       </c>
       <c r="R186" s="3" t="inlineStr"/>
-      <c r="S186" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S186" s="3" t="inlineStr"/>
       <c r="T186" s="3" t="inlineStr"/>
       <c r="U186" s="4" t="inlineStr">
         <is>
@@ -19718,11 +19066,7 @@
         </is>
       </c>
       <c r="R187" s="3" t="inlineStr"/>
-      <c r="S187" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S187" s="3" t="inlineStr"/>
       <c r="T187" s="3" t="inlineStr"/>
       <c r="U187" s="4" t="inlineStr">
         <is>
@@ -19830,11 +19174,7 @@
         </is>
       </c>
       <c r="R188" s="3" t="inlineStr"/>
-      <c r="S188" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S188" s="3" t="inlineStr"/>
       <c r="T188" s="3" t="inlineStr"/>
       <c r="U188" s="4" t="inlineStr">
         <is>
@@ -19922,11 +19262,7 @@
         </is>
       </c>
       <c r="R189" s="3" t="inlineStr"/>
-      <c r="S189" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S189" s="3" t="inlineStr"/>
       <c r="T189" s="3" t="inlineStr"/>
       <c r="U189" s="5" t="inlineStr">
         <is>
@@ -20032,11 +19368,7 @@
       </c>
       <c r="Q190" s="3" t="inlineStr"/>
       <c r="R190" s="3" t="inlineStr"/>
-      <c r="S190" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S190" s="3" t="inlineStr"/>
       <c r="T190" s="3" t="inlineStr"/>
       <c r="U190" s="4" t="inlineStr">
         <is>
@@ -20144,11 +19476,7 @@
         </is>
       </c>
       <c r="R191" s="3" t="inlineStr"/>
-      <c r="S191" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S191" s="3" t="inlineStr"/>
       <c r="T191" s="3" t="inlineStr"/>
       <c r="U191" s="4" t="inlineStr">
         <is>
@@ -20252,11 +19580,7 @@
       </c>
       <c r="Q192" s="3" t="inlineStr"/>
       <c r="R192" s="3" t="inlineStr"/>
-      <c r="S192" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S192" s="3" t="inlineStr"/>
       <c r="T192" s="3" t="inlineStr"/>
       <c r="U192" s="4" t="inlineStr">
         <is>
@@ -20352,11 +19676,7 @@
       </c>
       <c r="Q193" s="3" t="inlineStr"/>
       <c r="R193" s="3" t="inlineStr"/>
-      <c r="S193" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S193" s="3" t="inlineStr"/>
       <c r="T193" s="3" t="inlineStr"/>
       <c r="U193" s="4" t="inlineStr">
         <is>
@@ -20440,11 +19760,7 @@
       </c>
       <c r="Q194" s="3" t="inlineStr"/>
       <c r="R194" s="3" t="inlineStr"/>
-      <c r="S194" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S194" s="3" t="inlineStr"/>
       <c r="T194" s="3" t="inlineStr"/>
       <c r="U194" s="6" t="inlineStr">
         <is>
@@ -20543,15 +19859,19 @@
       </c>
       <c r="R195" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 자격, 작업자)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S195" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T195" s="3" t="inlineStr"/>
+          <t>제16조(배치, 전직, 승진), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T195" s="3" t="inlineStr">
+        <is>
+          <t>제16조③ 인사발령 기준은 '별도의 규정'으로 위임. 자격인증 기준·평가는 취업규칙에 없음 → SH 문서 필요</t>
+        </is>
+      </c>
       <c r="U195" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -20659,15 +19979,19 @@
       </c>
       <c r="R196" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 자격)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S196" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T196" s="3" t="inlineStr"/>
+          <t>제16조(배치, 전직, 승진), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T196" s="3" t="inlineStr">
+        <is>
+          <t>제16조③ 인사발령 기준은 '별도의 규정'으로 위임. 자격인증 기준·평가는 취업규칙에 없음 → SH 문서 필요</t>
+        </is>
+      </c>
       <c r="U196" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -20775,15 +20099,19 @@
       </c>
       <c r="R197" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 교육, 자격, 작업자)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S197" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T197" s="3" t="inlineStr"/>
+          <t>제16조(배치, 전직, 승진), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T197" s="3" t="inlineStr">
+        <is>
+          <t>제16조③ 인사발령 기준은 '별도의 규정'으로 위임. 자격인증 기준·평가는 취업규칙에 없음 → SH 문서 필요</t>
+        </is>
+      </c>
       <c r="U197" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -20882,11 +20210,7 @@
         </is>
       </c>
       <c r="R198" s="3" t="inlineStr"/>
-      <c r="S198" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S198" s="3" t="inlineStr"/>
       <c r="T198" s="3" t="inlineStr"/>
       <c r="U198" s="4" t="inlineStr">
         <is>
@@ -20986,11 +20310,7 @@
         </is>
       </c>
       <c r="R199" s="3" t="inlineStr"/>
-      <c r="S199" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S199" s="3" t="inlineStr"/>
       <c r="T199" s="3" t="inlineStr"/>
       <c r="U199" s="4" t="inlineStr">
         <is>
@@ -21098,11 +20418,7 @@
         </is>
       </c>
       <c r="R200" s="3" t="inlineStr"/>
-      <c r="S200" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S200" s="3" t="inlineStr"/>
       <c r="T200" s="3" t="inlineStr"/>
       <c r="U200" s="4" t="inlineStr">
         <is>
@@ -21193,16 +20509,8 @@
           <t>2025년 작업자 LEVEL 평가.xlsx</t>
         </is>
       </c>
-      <c r="R201" s="3" t="inlineStr">
-        <is>
-          <t>후보(키워드: 자격)</t>
-        </is>
-      </c>
-      <c r="S201" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="R201" s="3" t="inlineStr"/>
+      <c r="S201" s="3" t="inlineStr"/>
       <c r="T201" s="3" t="inlineStr"/>
       <c r="U201" s="6" t="inlineStr">
         <is>
@@ -21303,15 +20611,19 @@
       </c>
       <c r="R202" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 교육, 자격)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S202" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T202" s="3" t="inlineStr"/>
+          <t>제16조(배치, 전직, 승진), 제68조(직무교육), 제67조(교육시간)</t>
+        </is>
+      </c>
+      <c r="T202" s="3" t="inlineStr">
+        <is>
+          <t>제16조③ 인사발령 기준은 '별도의 규정'으로 위임. 자격인증 기준·평가는 취업규칙에 없음 → SH 문서 필요 / 교육시간의 근로시간 처리·직무교육 의무만 규정. 교육 계획·이력 증빙은 취업규칙에 없음</t>
+        </is>
+      </c>
       <c r="U202" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -21411,15 +20723,19 @@
       </c>
       <c r="R203" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 교육, 자격, 작업자)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S203" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T203" s="3" t="inlineStr"/>
+          <t>제16조(배치, 전직, 승진), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T203" s="3" t="inlineStr">
+        <is>
+          <t>제16조③ 인사발령 기준은 '별도의 규정'으로 위임. 자격인증 기준·평가는 취업규칙에 없음 → SH 문서 필요</t>
+        </is>
+      </c>
       <c r="U203" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -21519,15 +20835,19 @@
       </c>
       <c r="R204" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 교육, 자격, 작업자)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S204" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T204" s="3" t="inlineStr"/>
+          <t>제67조(교육시간), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T204" s="3" t="inlineStr">
+        <is>
+          <t>교육시간의 근로시간 처리·직무교육 의무만 규정. 교육 계획·이력 증빙은 취업규칙에 없음</t>
+        </is>
+      </c>
       <c r="U204" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -21637,15 +20957,19 @@
       </c>
       <c r="R205" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 교육)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S205" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T205" s="3" t="inlineStr"/>
+          <t>제67조(교육시간), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T205" s="3" t="inlineStr">
+        <is>
+          <t>교육시간의 근로시간 처리·직무교육 의무만 규정. 교육 계획·이력 증빙은 취업규칙에 없음</t>
+        </is>
+      </c>
       <c r="U205" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -21753,15 +21077,19 @@
       </c>
       <c r="R206" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 교육)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S206" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T206" s="3" t="inlineStr"/>
+          <t>제67조(교육시간), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T206" s="3" t="inlineStr">
+        <is>
+          <t>교육시간의 근로시간 처리·직무교육 의무만 규정. 교육 계획·이력 증빙은 취업규칙에 없음</t>
+        </is>
+      </c>
       <c r="U206" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -21861,15 +21189,19 @@
       </c>
       <c r="R207" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 교육, 작업자)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S207" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T207" s="3" t="inlineStr"/>
+          <t>제67조(교육시간), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T207" s="3" t="inlineStr">
+        <is>
+          <t>교육시간의 근로시간 처리·직무교육 의무만 규정. 교육 계획·이력 증빙은 취업규칙에 없음</t>
+        </is>
+      </c>
       <c r="U207" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -21969,15 +21301,19 @@
       </c>
       <c r="R208" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 교육, 작업자)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S208" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T208" s="3" t="inlineStr"/>
+          <t>제67조(교육시간), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T208" s="3" t="inlineStr">
+        <is>
+          <t>교육시간의 근로시간 처리·직무교육 의무만 규정. 교육 계획·이력 증빙은 취업규칙에 없음</t>
+        </is>
+      </c>
       <c r="U208" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -22078,11 +21414,7 @@
         </is>
       </c>
       <c r="R209" s="3" t="inlineStr"/>
-      <c r="S209" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S209" s="3" t="inlineStr"/>
       <c r="T209" s="3" t="inlineStr"/>
       <c r="U209" s="4" t="inlineStr">
         <is>
@@ -22182,11 +21514,7 @@
         </is>
       </c>
       <c r="R210" s="3" t="inlineStr"/>
-      <c r="S210" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S210" s="3" t="inlineStr"/>
       <c r="T210" s="3" t="inlineStr"/>
       <c r="U210" s="4" t="inlineStr">
         <is>
@@ -22294,11 +21622,7 @@
         </is>
       </c>
       <c r="R211" s="3" t="inlineStr"/>
-      <c r="S211" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S211" s="3" t="inlineStr"/>
       <c r="T211" s="3" t="inlineStr"/>
       <c r="U211" s="4" t="inlineStr">
         <is>
@@ -22398,11 +21722,7 @@
         </is>
       </c>
       <c r="R212" s="3" t="inlineStr"/>
-      <c r="S212" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S212" s="3" t="inlineStr"/>
       <c r="T212" s="3" t="inlineStr"/>
       <c r="U212" s="4" t="inlineStr">
         <is>
@@ -22510,11 +21830,7 @@
         </is>
       </c>
       <c r="R213" s="3" t="inlineStr"/>
-      <c r="S213" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S213" s="3" t="inlineStr"/>
       <c r="T213" s="3" t="inlineStr"/>
       <c r="U213" s="4" t="inlineStr">
         <is>
@@ -22624,11 +21940,7 @@
         </is>
       </c>
       <c r="R214" s="3" t="inlineStr"/>
-      <c r="S214" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S214" s="3" t="inlineStr"/>
       <c r="T214" s="3" t="inlineStr"/>
       <c r="U214" s="4" t="inlineStr">
         <is>
@@ -22728,11 +22040,7 @@
         </is>
       </c>
       <c r="R215" s="3" t="inlineStr"/>
-      <c r="S215" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S215" s="3" t="inlineStr"/>
       <c r="T215" s="3" t="inlineStr"/>
       <c r="U215" s="4" t="inlineStr">
         <is>
@@ -22832,11 +22140,7 @@
         </is>
       </c>
       <c r="R216" s="3" t="inlineStr"/>
-      <c r="S216" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S216" s="3" t="inlineStr"/>
       <c r="T216" s="3" t="inlineStr"/>
       <c r="U216" s="4" t="inlineStr">
         <is>
@@ -22944,11 +22248,7 @@
         </is>
       </c>
       <c r="R217" s="3" t="inlineStr"/>
-      <c r="S217" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S217" s="3" t="inlineStr"/>
       <c r="T217" s="3" t="inlineStr"/>
       <c r="U217" s="4" t="inlineStr">
         <is>
@@ -23044,11 +22344,7 @@
         </is>
       </c>
       <c r="R218" s="3" t="inlineStr"/>
-      <c r="S218" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S218" s="3" t="inlineStr"/>
       <c r="T218" s="3" t="inlineStr"/>
       <c r="U218" s="4" t="inlineStr">
         <is>
@@ -23150,11 +22446,7 @@
         </is>
       </c>
       <c r="R219" s="3" t="inlineStr"/>
-      <c r="S219" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S219" s="3" t="inlineStr"/>
       <c r="T219" s="3" t="inlineStr"/>
       <c r="U219" s="4" t="inlineStr">
         <is>
@@ -23262,11 +22554,7 @@
         </is>
       </c>
       <c r="R220" s="3" t="inlineStr"/>
-      <c r="S220" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S220" s="3" t="inlineStr"/>
       <c r="T220" s="3" t="inlineStr"/>
       <c r="U220" s="4" t="inlineStr">
         <is>
@@ -23362,11 +22650,7 @@
         </is>
       </c>
       <c r="R221" s="3" t="inlineStr"/>
-      <c r="S221" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S221" s="3" t="inlineStr"/>
       <c r="T221" s="3" t="inlineStr"/>
       <c r="U221" s="4" t="inlineStr">
         <is>
@@ -23462,11 +22746,7 @@
         </is>
       </c>
       <c r="R222" s="3" t="inlineStr"/>
-      <c r="S222" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S222" s="3" t="inlineStr"/>
       <c r="T222" s="3" t="inlineStr"/>
       <c r="U222" s="4" t="inlineStr">
         <is>
@@ -23576,11 +22856,7 @@
         </is>
       </c>
       <c r="R223" s="3" t="inlineStr"/>
-      <c r="S223" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S223" s="3" t="inlineStr"/>
       <c r="T223" s="3" t="inlineStr"/>
       <c r="U223" s="4" t="inlineStr">
         <is>
@@ -23688,11 +22964,7 @@
         </is>
       </c>
       <c r="R224" s="3" t="inlineStr"/>
-      <c r="S224" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S224" s="3" t="inlineStr"/>
       <c r="T224" s="3" t="inlineStr"/>
       <c r="U224" s="4" t="inlineStr">
         <is>
@@ -23792,11 +23064,7 @@
         </is>
       </c>
       <c r="R225" s="3" t="inlineStr"/>
-      <c r="S225" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S225" s="3" t="inlineStr"/>
       <c r="T225" s="3" t="inlineStr"/>
       <c r="U225" s="4" t="inlineStr">
         <is>
@@ -23900,11 +23168,7 @@
         </is>
       </c>
       <c r="R226" s="3" t="inlineStr"/>
-      <c r="S226" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S226" s="3" t="inlineStr"/>
       <c r="T226" s="3" t="inlineStr"/>
       <c r="U226" s="4" t="inlineStr">
         <is>
@@ -24000,11 +23264,7 @@
         </is>
       </c>
       <c r="R227" s="3" t="inlineStr"/>
-      <c r="S227" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S227" s="3" t="inlineStr"/>
       <c r="T227" s="3" t="inlineStr"/>
       <c r="U227" s="4" t="inlineStr">
         <is>
@@ -24094,11 +23354,7 @@
       </c>
       <c r="Q228" s="3" t="inlineStr"/>
       <c r="R228" s="3" t="inlineStr"/>
-      <c r="S228" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S228" s="3" t="inlineStr"/>
       <c r="T228" s="3" t="inlineStr"/>
       <c r="U228" s="6" t="inlineStr">
         <is>
@@ -24202,11 +23458,7 @@
       </c>
       <c r="Q229" s="3" t="inlineStr"/>
       <c r="R229" s="3" t="inlineStr"/>
-      <c r="S229" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S229" s="3" t="inlineStr"/>
       <c r="T229" s="3" t="inlineStr"/>
       <c r="U229" s="4" t="inlineStr">
         <is>
@@ -24301,16 +23553,8 @@
         </is>
       </c>
       <c r="Q230" s="3" t="inlineStr"/>
-      <c r="R230" s="3" t="inlineStr">
-        <is>
-          <t>후보(키워드: 교육)</t>
-        </is>
-      </c>
-      <c r="S230" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="R230" s="3" t="inlineStr"/>
+      <c r="S230" s="3" t="inlineStr"/>
       <c r="T230" s="3" t="inlineStr"/>
       <c r="U230" s="4" t="inlineStr">
         <is>
@@ -24420,11 +23664,7 @@
         </is>
       </c>
       <c r="R231" s="3" t="inlineStr"/>
-      <c r="S231" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S231" s="3" t="inlineStr"/>
       <c r="T231" s="3" t="inlineStr"/>
       <c r="U231" s="4" t="inlineStr">
         <is>
@@ -24528,11 +23768,7 @@
       </c>
       <c r="Q232" s="3" t="inlineStr"/>
       <c r="R232" s="3" t="inlineStr"/>
-      <c r="S232" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S232" s="3" t="inlineStr"/>
       <c r="T232" s="3" t="inlineStr"/>
       <c r="U232" s="4" t="inlineStr">
         <is>
@@ -24640,11 +23876,7 @@
         </is>
       </c>
       <c r="R233" s="3" t="inlineStr"/>
-      <c r="S233" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S233" s="3" t="inlineStr"/>
       <c r="T233" s="3" t="inlineStr"/>
       <c r="U233" s="4" t="inlineStr">
         <is>
@@ -24740,11 +23972,7 @@
       </c>
       <c r="Q234" s="3" t="inlineStr"/>
       <c r="R234" s="3" t="inlineStr"/>
-      <c r="S234" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S234" s="3" t="inlineStr"/>
       <c r="T234" s="3" t="inlineStr"/>
       <c r="U234" s="5" t="inlineStr">
         <is>
@@ -24848,11 +24076,7 @@
       </c>
       <c r="Q235" s="3" t="inlineStr"/>
       <c r="R235" s="3" t="inlineStr"/>
-      <c r="S235" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S235" s="3" t="inlineStr"/>
       <c r="T235" s="3" t="inlineStr"/>
       <c r="U235" s="4" t="inlineStr">
         <is>
@@ -24956,11 +24180,7 @@
       </c>
       <c r="Q236" s="3" t="inlineStr"/>
       <c r="R236" s="3" t="inlineStr"/>
-      <c r="S236" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S236" s="3" t="inlineStr"/>
       <c r="T236" s="3" t="inlineStr"/>
       <c r="U236" s="4" t="inlineStr">
         <is>
@@ -25055,16 +24275,8 @@
         </is>
       </c>
       <c r="Q237" s="3" t="inlineStr"/>
-      <c r="R237" s="3" t="inlineStr">
-        <is>
-          <t>후보(키워드: 교육)</t>
-        </is>
-      </c>
-      <c r="S237" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="R237" s="3" t="inlineStr"/>
+      <c r="S237" s="3" t="inlineStr"/>
       <c r="T237" s="3" t="inlineStr"/>
       <c r="U237" s="6" t="inlineStr">
         <is>
@@ -25165,15 +24377,19 @@
       <c r="Q238" s="3" t="inlineStr"/>
       <c r="R238" s="3" t="inlineStr">
         <is>
-          <t>후보(키워드: 자격)</t>
+          <t>부분</t>
         </is>
       </c>
       <c r="S238" s="3" t="inlineStr">
         <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
-      <c r="T238" s="3" t="inlineStr"/>
+          <t>제16조(배치, 전직, 승진), 제68조(직무교육)</t>
+        </is>
+      </c>
+      <c r="T238" s="3" t="inlineStr">
+        <is>
+          <t>제16조③ 인사발령 기준은 '별도의 규정'으로 위임. 자격인증 기준·평가는 취업규칙에 없음 → SH 문서 필요</t>
+        </is>
+      </c>
       <c r="U238" s="4" t="inlineStr">
         <is>
           <t>A 양식 틀 배포(항목 미작성)</t>
@@ -25274,11 +24490,7 @@
         </is>
       </c>
       <c r="R239" s="3" t="inlineStr"/>
-      <c r="S239" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S239" s="3" t="inlineStr"/>
       <c r="T239" s="3" t="inlineStr"/>
       <c r="U239" s="4" t="inlineStr">
         <is>
@@ -25377,16 +24589,8 @@
           <t>정성품질 6차.7z</t>
         </is>
       </c>
-      <c r="R240" s="3" t="inlineStr">
-        <is>
-          <t>후보(키워드: 교육)</t>
-        </is>
-      </c>
-      <c r="S240" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="R240" s="3" t="inlineStr"/>
+      <c r="S240" s="3" t="inlineStr"/>
       <c r="T240" s="3" t="inlineStr"/>
       <c r="U240" s="4" t="inlineStr">
         <is>
@@ -25486,11 +24690,7 @@
         </is>
       </c>
       <c r="R241" s="3" t="inlineStr"/>
-      <c r="S241" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S241" s="3" t="inlineStr"/>
       <c r="T241" s="3" t="inlineStr"/>
       <c r="U241" s="4" t="inlineStr">
         <is>
@@ -25589,16 +24789,8 @@
           <t>정성품질개요-V1.pptx</t>
         </is>
       </c>
-      <c r="R242" s="3" t="inlineStr">
-        <is>
-          <t>후보(키워드: 작업자)</t>
-        </is>
-      </c>
-      <c r="S242" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="R242" s="3" t="inlineStr"/>
+      <c r="S242" s="3" t="inlineStr"/>
       <c r="T242" s="3" t="inlineStr"/>
       <c r="U242" s="4" t="inlineStr">
         <is>
@@ -25706,11 +24898,7 @@
         </is>
       </c>
       <c r="R243" s="3" t="inlineStr"/>
-      <c r="S243" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S243" s="3" t="inlineStr"/>
       <c r="T243" s="3" t="inlineStr"/>
       <c r="U243" s="4" t="inlineStr">
         <is>
@@ -25810,11 +24998,7 @@
         </is>
       </c>
       <c r="R244" s="3" t="inlineStr"/>
-      <c r="S244" s="3" t="inlineStr">
-        <is>
-          <t>취업규칙 파일 미제공 — 조항 입력 대기</t>
-        </is>
-      </c>
+      <c r="S244" s="3" t="inlineStr"/>
       <c r="T244" s="3" t="inlineStr"/>
       <c r="U244" s="4" t="inlineStr">
         <is>
@@ -25854,7 +25038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -25953,28 +25137,58 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>취업규칙 연계 후보(키워드 추정)</t>
+          <t>취업규칙 관련도: 직접</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>요구사항·서류명에 교육/자격/인사 등 키워드. 파일 확인 후 확정</t>
+          <t>키워드 추정 — 담당자 확인 필요</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>취업규칙 관련도: 부분</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>키워드 추정 — 담당자 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>취업규칙 관련도: 범위 밖</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>키워드 추정 — 담당자 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>연계 QP/WI 없음</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>104</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>연계 절차 확인 필요</t>
         </is>
@@ -25991,7 +25205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -26028,12 +25242,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5. 취업규칙: 저장소에 파일 없음 → 조항·비고 칸 공란. 파일 제공 시 후보 행부터 조항 입력.</t>
+          <t>5. 취업규칙: 2026-09-28 검토 반영본(음주금지 반영) 조문 기준. 개정일·시행일 공란, 회사 최종 확인사항 7건 미확인 → 승인·시행 전 초안으로 취급. 현재 시행본은 2025-07 수정본(시행이력 2025-07-22 기재).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>5-1. 관련도: 직접=조문이 요구사항의 근거, 부분=일부 근거(양식·기준은 별도 SH 문서 필요), 범위 밖=취업규칙에 조항 없음. 키워드로 추정한 것이므로 조문을 읽고 확정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>6. 확인자·확인일자·실제 기록 증빙 위치·메모는 사람이 입력(임의 생성 금지).</t>
         </is>
